--- a/aps-system/src/main/resources/static/template-safety-stock.xlsx
+++ b/aps-system/src/main/resources/static/template-safety-stock.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -462,12 +462,13 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>说明：按版本号进行全删全导，安全天数必填且≥0，版本号必填</t>
+          <t>说明：按版本号进行全删全导，年月格式 YYYYMM（如202501），安全天数必填且≥0，版本号必填</t>
         </is>
       </c>
     </row>
@@ -479,20 +480,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>日当量</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>安全天数</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>最大天数</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>版本号</t>
         </is>
@@ -504,6 +510,7 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -511,10 +518,11 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
